--- a/education_surveys/034_student_quiz_feedback_survey--education_surveys.xlsx
+++ b/education_surveys/034_student_quiz_feedback_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Welcome to the Quiz Feedback Survey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,51 +538,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quiz_experience</t>
+          <t>technical_issues</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quiz Experience</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>How would you rate your experience taking the quiz?</t>
-        </is>
-      </c>
+          <t>Technical Issues</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>technical_issues</t>
+          <t>learning_objectives</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Technical Issues</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Were there any technical issues that affected your ability to complete the quiz?</t>
-        </is>
-      </c>
+          <t>Learning Objectives</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -592,81 +584,69 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>learning_objectives</t>
+          <t>question_difficulty</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Learning Objectives</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Were the learning objectives clear and achievable?</t>
-        </is>
-      </c>
+          <t>Question Difficulty</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_difficulty</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Question Difficulty</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Were the questions clear and concise?</t>
-        </is>
-      </c>
+          <t>Time Management</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>time_management</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Time Management</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>How long did it take you to complete the quiz?</t>
-        </is>
-      </c>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -678,19 +658,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>overall_experience</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Any additional feedback or comments?</t>
-        </is>
-      </c>
+          <t>Overall Experience</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -700,416 +676,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>overall_experience</t>
+          <t>improvement_areas</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Overall Experience</t>
+          <t>Areas for Improvement</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>improvement_areas</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Areas for Improvement</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>What could we do to improve the quiz?</t>
-        </is>
-      </c>
+          <t>Contact Information</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>email_address</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Email Address</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1126,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1159,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>no_issues</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>No issues</t>
         </is>
       </c>
     </row>
@@ -1176,46 +803,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>issues_with_loading_times</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Issues with loading times</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>learning_objectives_choices</t>
+          <t>technical_issues_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'too_broad'}</t>
+          <t>issues_with_question_display</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Too broad'}</t>
+          <t>Issues with question display</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>learning_objectives_choices</t>
+          <t>technical_issues_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'adequate'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Adequate'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1227,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'too_narrow'}</t>
+          <t>clear_and_achievable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Too narrow'}</t>
+          <t>Clear and achievable</t>
         </is>
       </c>
     </row>
@@ -1244,46 +871,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_clear'}</t>
+          <t>clear_and_somewhat_achievable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not clear'}</t>
+          <t>Clear and somewhat achievable</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time_management_choices</t>
+          <t>learning_objectives_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_5_minutes'}</t>
+          <t>not_clear_or_too_broad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 5 minutes'}</t>
+          <t>Not clear or too broad</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time_management_choices</t>
+          <t>learning_objectives_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'5-10_minutes'}</t>
+          <t>not_clear_or_too_narrow</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '5-10 minutes'}</t>
+          <t>Not clear or too narrow</t>
         </is>
       </c>
     </row>
@@ -1295,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'10-15_minutes'}</t>
+          <t>less_than_5_minutes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '10-15 minutes'}</t>
+          <t>Less than 5 minutes</t>
         </is>
       </c>
     </row>
@@ -1312,46 +939,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_15_minutes'}</t>
+          <t>5-10_minutes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'More than 15 minutes'}</t>
+          <t>5-10 minutes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>improvement_areas_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'clearer_instructions'}</t>
+          <t>10-15_minutes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Clearer instructions'}</t>
+          <t>10-15 minutes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>improvement_areas_choices</t>
+          <t>time_management_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'more_feedback'}</t>
+          <t>more_than_15_minutes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'More feedback'}</t>
+          <t>More than 15 minutes</t>
         </is>
       </c>
     </row>
@@ -1363,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'less_questions'}</t>
+          <t>clearer_instructions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Less questions'}</t>
+          <t>Clearer instructions</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1007,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>more_feedback</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>More feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>improvement_areas_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>less_questions</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Less questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>improvement_areas_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
